--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/68.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/68.xlsx
@@ -426,13 +426,13 @@
         <v>-4.003182041699267</v>
       </c>
       <c r="E2">
-        <v>-29.95249524549632</v>
+        <v>-32.8472656489745</v>
       </c>
       <c r="F2">
-        <v>-6.209291857399811</v>
+        <v>-7.034981087929378</v>
       </c>
       <c r="G2">
-        <v>-19.39162758440657</v>
+        <v>-20.04859541503832</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.782073968574314</v>
       </c>
       <c r="E3">
-        <v>-31.77330181026342</v>
+        <v>-33.92476396164857</v>
       </c>
       <c r="F3">
-        <v>-5.961943916408732</v>
+        <v>-6.83653402634228</v>
       </c>
       <c r="G3">
-        <v>-19.22594305652989</v>
+        <v>-19.39163420549765</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.66402102321937</v>
       </c>
       <c r="E4">
-        <v>-32.10819604855266</v>
+        <v>-32.36280044268591</v>
       </c>
       <c r="F4">
-        <v>-5.822288769520493</v>
+        <v>-7.145354304294099</v>
       </c>
       <c r="G4">
-        <v>-18.24029929894099</v>
+        <v>-20.12924195964773</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.655086912843563</v>
       </c>
       <c r="E5">
-        <v>-32.50309256744354</v>
+        <v>-33.83512281866674</v>
       </c>
       <c r="F5">
-        <v>-5.851108257916702</v>
+        <v>-6.919701946565104</v>
       </c>
       <c r="G5">
-        <v>-19.14996438113085</v>
+        <v>-19.25014645496751</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.726889728293584</v>
       </c>
       <c r="E6">
-        <v>-32.95750682021723</v>
+        <v>-34.14125219005926</v>
       </c>
       <c r="F6">
-        <v>-6.069022232616382</v>
+        <v>-7.349808758344937</v>
       </c>
       <c r="G6">
-        <v>-19.14411464716296</v>
+        <v>-19.66234744588047</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.857166853376503</v>
       </c>
       <c r="E7">
-        <v>-32.98232512201626</v>
+        <v>-34.4753154533681</v>
       </c>
       <c r="F7">
-        <v>-5.898011292308357</v>
+        <v>-6.412461925953228</v>
       </c>
       <c r="G7">
-        <v>-17.86505061733737</v>
+        <v>-19.4654428182957</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.017666441453344</v>
       </c>
       <c r="E8">
-        <v>-33.47536952231238</v>
+        <v>-34.83561895931439</v>
       </c>
       <c r="F8">
-        <v>-5.913343941128684</v>
+        <v>-6.709259500447989</v>
       </c>
       <c r="G8">
-        <v>-18.5207985119379</v>
+        <v>-19.43852808306142</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.185488488287864</v>
       </c>
       <c r="E9">
-        <v>-33.56372231443904</v>
+        <v>-35.35754823106844</v>
       </c>
       <c r="F9">
-        <v>-5.827128574798076</v>
+        <v>-6.964866071861606</v>
       </c>
       <c r="G9">
-        <v>-18.09528581741153</v>
+        <v>-19.27955568626562</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.341900496224572</v>
       </c>
       <c r="E10">
-        <v>-33.76094415018409</v>
+        <v>-35.92023829736552</v>
       </c>
       <c r="F10">
-        <v>-5.750525511521228</v>
+        <v>-6.525047579481819</v>
       </c>
       <c r="G10">
-        <v>-18.13054147213199</v>
+        <v>-19.67737070153768</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.470214519113001</v>
       </c>
       <c r="E11">
-        <v>-33.69296269838095</v>
+        <v>-36.33177242976058</v>
       </c>
       <c r="F11">
-        <v>-5.674386474077603</v>
+        <v>-6.455327698039949</v>
       </c>
       <c r="G11">
-        <v>-18.38897093329135</v>
+        <v>-18.88976377810798</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.563813868636288</v>
       </c>
       <c r="E12">
-        <v>-34.37314855128105</v>
+        <v>-36.21495138578471</v>
       </c>
       <c r="F12">
-        <v>-5.47883759431576</v>
+        <v>-6.150892305841503</v>
       </c>
       <c r="G12">
-        <v>-18.11918961147784</v>
+        <v>-19.90825973435584</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.620707698719242</v>
       </c>
       <c r="E13">
-        <v>-35.76602564350831</v>
+        <v>-35.79548563116521</v>
       </c>
       <c r="F13">
-        <v>-5.556458980496235</v>
+        <v>-6.453552363708742</v>
       </c>
       <c r="G13">
-        <v>-17.00102968177022</v>
+        <v>-20.02206966890491</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.647912894374158</v>
       </c>
       <c r="E14">
-        <v>-35.97801256875538</v>
+        <v>-37.96954033937464</v>
       </c>
       <c r="F14">
-        <v>-5.631879807307208</v>
+        <v>-6.829264024337455</v>
       </c>
       <c r="G14">
-        <v>-16.68429985839152</v>
+        <v>-18.82888119036802</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.651845349548656</v>
       </c>
       <c r="E15">
-        <v>-36.48414425893367</v>
+        <v>-37.1840674657962</v>
       </c>
       <c r="F15">
-        <v>-5.448314830207495</v>
+        <v>-6.090443438828616</v>
       </c>
       <c r="G15">
-        <v>-17.04791859351568</v>
+        <v>-18.9347689894416</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.644759942379086</v>
       </c>
       <c r="E16">
-        <v>-36.4706426136798</v>
+        <v>-37.35229574670715</v>
       </c>
       <c r="F16">
-        <v>-5.688817202379087</v>
+        <v>-5.813777933930921</v>
       </c>
       <c r="G16">
-        <v>-16.30190536424139</v>
+        <v>-18.77921307564233</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.638948919165506</v>
       </c>
       <c r="E17">
-        <v>-37.04041974179889</v>
+        <v>-37.31418410945859</v>
       </c>
       <c r="F17">
-        <v>-5.355276858793173</v>
+        <v>-5.769489598005658</v>
       </c>
       <c r="G17">
-        <v>-16.10388177226434</v>
+        <v>-17.94791191691256</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.642640032522892</v>
       </c>
       <c r="E18">
-        <v>-36.58531716097604</v>
+        <v>-38.61980656450606</v>
       </c>
       <c r="F18">
-        <v>-5.302751668401709</v>
+        <v>-5.842444594706291</v>
       </c>
       <c r="G18">
-        <v>-16.29545311098535</v>
+        <v>-17.92112794822709</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.662787786073567</v>
       </c>
       <c r="E19">
-        <v>-38.09251784376394</v>
+        <v>-38.63301385894944</v>
       </c>
       <c r="F19">
-        <v>-5.008682027346293</v>
+        <v>-5.657733806376757</v>
       </c>
       <c r="G19">
-        <v>-15.83440667591321</v>
+        <v>-17.27103943122594</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.70255260345706</v>
       </c>
       <c r="E20">
-        <v>-38.51020164386141</v>
+        <v>-38.47696490888212</v>
       </c>
       <c r="F20">
-        <v>-4.886586219795489</v>
+        <v>-5.340593529398177</v>
       </c>
       <c r="G20">
-        <v>-15.38621343389729</v>
+        <v>-17.70452722995642</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.76497630854865</v>
       </c>
       <c r="E21">
-        <v>-38.98805301386181</v>
+        <v>-38.64500072964774</v>
       </c>
       <c r="F21">
-        <v>-5.103305288381969</v>
+        <v>-5.062261174024482</v>
       </c>
       <c r="G21">
-        <v>-16.07898812508179</v>
+        <v>-17.61637402333671</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.844612970797928</v>
       </c>
       <c r="E22">
-        <v>-38.65833029288932</v>
+        <v>-38.95214900769199</v>
       </c>
       <c r="F22">
-        <v>-4.730176256174858</v>
+        <v>-5.341485155828569</v>
       </c>
       <c r="G22">
-        <v>-15.01577828550777</v>
+        <v>-16.68481630349565</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.939112385683771</v>
       </c>
       <c r="E23">
-        <v>-39.14642733533206</v>
+        <v>-41.0448383591686</v>
       </c>
       <c r="F23">
-        <v>-4.640518705037042</v>
+        <v>-5.539056428044429</v>
       </c>
       <c r="G23">
-        <v>-15.65754740156872</v>
+        <v>-16.67797506113875</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.042649732870662</v>
       </c>
       <c r="E24">
-        <v>-40.61355555162609</v>
+        <v>-42.54367495046434</v>
       </c>
       <c r="F24">
-        <v>-4.280520970427798</v>
+        <v>-5.031427211703835</v>
       </c>
       <c r="G24">
-        <v>-15.04948957073417</v>
+        <v>-16.73689780591947</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.150069629087763</v>
       </c>
       <c r="E25">
-        <v>-41.23153149284582</v>
+        <v>-40.6976923344516</v>
       </c>
       <c r="F25">
-        <v>-4.137896374948109</v>
+        <v>-5.389925968664116</v>
       </c>
       <c r="G25">
-        <v>-15.37903617116815</v>
+        <v>-16.83660647174401</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.253363732306298</v>
       </c>
       <c r="E26">
-        <v>-40.12354522891511</v>
+        <v>-40.56247210058257</v>
       </c>
       <c r="F26">
-        <v>-4.297232235247515</v>
+        <v>-4.849365963370831</v>
       </c>
       <c r="G26">
-        <v>-15.39534226322183</v>
+        <v>-17.19592315293988</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.345993267276729</v>
       </c>
       <c r="E27">
-        <v>-39.94654529385131</v>
+        <v>-40.16816201907568</v>
       </c>
       <c r="F27">
-        <v>-4.4963294081129</v>
+        <v>-5.04915996683901</v>
       </c>
       <c r="G27">
-        <v>-15.15063997914106</v>
+        <v>-16.80168683739577</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.423444258139494</v>
       </c>
       <c r="E28">
-        <v>-39.43301860561849</v>
+        <v>-42.49940911703936</v>
       </c>
       <c r="F28">
-        <v>-4.156746434606627</v>
+        <v>-5.289081910792594</v>
       </c>
       <c r="G28">
-        <v>-15.19895739128672</v>
+        <v>-16.6473409279911</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.477485004900323</v>
       </c>
       <c r="E29">
-        <v>-40.59274494932384</v>
+        <v>-40.82733348834319</v>
       </c>
       <c r="F29">
-        <v>-4.468890119421997</v>
+        <v>-4.568567777886797</v>
       </c>
       <c r="G29">
-        <v>-15.56377619916887</v>
+        <v>-17.69625417665378</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.503410673088876</v>
       </c>
       <c r="E30">
-        <v>-40.3052004352588</v>
+        <v>-40.08565322265593</v>
       </c>
       <c r="F30">
-        <v>-4.355245758488935</v>
+        <v>-5.079103094582224</v>
       </c>
       <c r="G30">
-        <v>-14.96034485572544</v>
+        <v>-17.45940119604663</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.493715240340449</v>
       </c>
       <c r="E31">
-        <v>-39.59627915054302</v>
+        <v>-41.16744226445227</v>
       </c>
       <c r="F31">
-        <v>-4.636865095490124</v>
+        <v>-4.880447775667245</v>
       </c>
       <c r="G31">
-        <v>-15.83290037769284</v>
+        <v>-16.78573331844202</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.4460601307333</v>
       </c>
       <c r="E32">
-        <v>-39.5565304699407</v>
+        <v>-41.75788055523136</v>
       </c>
       <c r="F32">
-        <v>-4.563517339722461</v>
+        <v>-5.032815329938717</v>
       </c>
       <c r="G32">
-        <v>-15.62677919132674</v>
+        <v>-17.7611789404972</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.35387176768316</v>
       </c>
       <c r="E33">
-        <v>-40.07739102182893</v>
+        <v>-41.79166749980259</v>
       </c>
       <c r="F33">
-        <v>-4.54484544697943</v>
+        <v>-5.281630574460451</v>
       </c>
       <c r="G33">
-        <v>-15.81486121504935</v>
+        <v>-16.82120581389531</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.21272947866427</v>
       </c>
       <c r="E34">
-        <v>-39.2921581573729</v>
+        <v>-40.20210293176317</v>
       </c>
       <c r="F34">
-        <v>-4.213332246965279</v>
+        <v>-5.342147936754181</v>
       </c>
       <c r="G34">
-        <v>-15.55173574504254</v>
+        <v>-17.81267116581503</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.020619151179752</v>
       </c>
       <c r="E35">
-        <v>-38.62790800450579</v>
+        <v>-40.41169203002318</v>
       </c>
       <c r="F35">
-        <v>-4.556256048100171</v>
+        <v>-5.127379202002564</v>
       </c>
       <c r="G35">
-        <v>-16.20270155661159</v>
+        <v>-16.85576459877977</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.779124691321805</v>
       </c>
       <c r="E36">
-        <v>-38.28745506437212</v>
+        <v>-39.75134995022468</v>
       </c>
       <c r="F36">
-        <v>-4.336274545327885</v>
+        <v>-5.151777775335824</v>
       </c>
       <c r="G36">
-        <v>-15.76076855621043</v>
+        <v>-16.65622477694573</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.490712315963663</v>
       </c>
       <c r="E37">
-        <v>-38.73540944897388</v>
+        <v>-40.05890579092962</v>
       </c>
       <c r="F37">
-        <v>-4.4370101193442</v>
+        <v>-4.843032723414988</v>
       </c>
       <c r="G37">
-        <v>-15.99815784519495</v>
+        <v>-17.13606517904432</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.158658390254611</v>
       </c>
       <c r="E38">
-        <v>-38.18136423955743</v>
+        <v>-40.46954328547116</v>
       </c>
       <c r="F38">
-        <v>-4.374651698923772</v>
+        <v>-5.342292053992486</v>
       </c>
       <c r="G38">
-        <v>-15.46734993924651</v>
+        <v>-17.11360478283313</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.793895975898916</v>
       </c>
       <c r="E39">
-        <v>-37.84920293533182</v>
+        <v>-39.46059021961419</v>
       </c>
       <c r="F39">
-        <v>-4.362664628849811</v>
+        <v>-5.609817200199221</v>
       </c>
       <c r="G39">
-        <v>-15.97175789979203</v>
+        <v>-16.83225972545094</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.406332249217039</v>
       </c>
       <c r="E40">
-        <v>-37.52879754963011</v>
+        <v>-39.62954758484037</v>
       </c>
       <c r="F40">
-        <v>-4.189951996535647</v>
+        <v>-5.03576260664735</v>
       </c>
       <c r="G40">
-        <v>-15.89106997336337</v>
+        <v>-16.19831508377205</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.005589844950218</v>
       </c>
       <c r="E41">
-        <v>-37.23221193720875</v>
+        <v>-40.90700066732313</v>
       </c>
       <c r="F41">
-        <v>-4.422524753188633</v>
+        <v>-4.818566842580323</v>
       </c>
       <c r="G41">
-        <v>-16.44695526177178</v>
+        <v>-17.23246329932959</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.600694728989352</v>
       </c>
       <c r="E42">
-        <v>-36.54303027069241</v>
+        <v>-37.28661023122589</v>
       </c>
       <c r="F42">
-        <v>-4.347269423645824</v>
+        <v>-4.828334348813795</v>
       </c>
       <c r="G42">
-        <v>-16.67565933453402</v>
+        <v>-16.82966094720261</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.2050981219706</v>
       </c>
       <c r="E43">
-        <v>-36.29976517547437</v>
+        <v>-38.70025490525233</v>
       </c>
       <c r="F43">
-        <v>-4.077985572019993</v>
+        <v>-4.734858482713855</v>
       </c>
       <c r="G43">
-        <v>-16.13059290894795</v>
+        <v>-17.34656787243165</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.826825602985451</v>
       </c>
       <c r="E44">
-        <v>-35.99995981803355</v>
+        <v>-38.18303977494027</v>
       </c>
       <c r="F44">
-        <v>-4.056733030487753</v>
+        <v>-4.832313409926337</v>
       </c>
       <c r="G44">
-        <v>-16.27355054169753</v>
+        <v>-16.96061288655402</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.471149877980779</v>
       </c>
       <c r="E45">
-        <v>-35.37877318874239</v>
+        <v>-36.95229563760962</v>
       </c>
       <c r="F45">
-        <v>-4.177733705398031</v>
+        <v>-4.97083145596729</v>
       </c>
       <c r="G45">
-        <v>-16.28075428879098</v>
+        <v>-17.78070784863336</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.145905779281451</v>
       </c>
       <c r="E46">
-        <v>-35.77644566219996</v>
+        <v>-38.70872768012068</v>
       </c>
       <c r="F46">
-        <v>-4.069745550141961</v>
+        <v>-4.547734918422149</v>
       </c>
       <c r="G46">
-        <v>-16.06551254946419</v>
+        <v>-16.72836321951922</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.8574791147887206</v>
       </c>
       <c r="E47">
-        <v>-34.97884100675498</v>
+        <v>-37.22715589597919</v>
       </c>
       <c r="F47">
-        <v>-4.002601962298033</v>
+        <v>-4.709949164222865</v>
       </c>
       <c r="G47">
-        <v>-16.65161815282784</v>
+        <v>-17.83000849280419</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.6082141933259771</v>
       </c>
       <c r="E48">
-        <v>-35.44558855848856</v>
+        <v>-38.29447193484701</v>
       </c>
       <c r="F48">
-        <v>-3.971704651740767</v>
+        <v>-4.549787401288559</v>
       </c>
       <c r="G48">
-        <v>-16.35944595625946</v>
+        <v>-16.84306700136389</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.3971167957479569</v>
       </c>
       <c r="E49">
-        <v>-34.0706623372277</v>
+        <v>-35.63445988816347</v>
       </c>
       <c r="F49">
-        <v>-3.818397168008482</v>
+        <v>-4.911076648071845</v>
       </c>
       <c r="G49">
-        <v>-16.90338845163495</v>
+        <v>-17.14544892037538</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.226488121022236</v>
       </c>
       <c r="E50">
-        <v>-34.07854641047505</v>
+        <v>-37.27133568839802</v>
       </c>
       <c r="F50">
-        <v>-3.991634798833615</v>
+        <v>-4.342925318319773</v>
       </c>
       <c r="G50">
-        <v>-16.78682248792444</v>
+        <v>-17.76214727506744</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.09370900427949984</v>
       </c>
       <c r="E51">
-        <v>-33.82802896413372</v>
+        <v>-37.27682646313232</v>
       </c>
       <c r="F51">
-        <v>-3.845944940554594</v>
+        <v>-4.142687877195272</v>
       </c>
       <c r="G51">
-        <v>-16.75413250599691</v>
+        <v>-16.37998292551233</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.005365639022445971</v>
       </c>
       <c r="E52">
-        <v>-33.32915415355273</v>
+        <v>-37.3158981368705</v>
       </c>
       <c r="F52">
-        <v>-4.060887882956909</v>
+        <v>-4.707380393228023</v>
       </c>
       <c r="G52">
-        <v>-17.17485153058242</v>
+        <v>-17.05604763808736</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.07398179652229178</v>
       </c>
       <c r="E53">
-        <v>-33.38917454805039</v>
+        <v>-36.05461397083213</v>
       </c>
       <c r="F53">
-        <v>-4.16733350865134</v>
+        <v>-5.069067942049042</v>
       </c>
       <c r="G53">
-        <v>-16.87459001598883</v>
+        <v>-18.0525648825</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.1146939029792355</v>
       </c>
       <c r="E54">
-        <v>-33.61755907767923</v>
+        <v>-35.30747462972862</v>
       </c>
       <c r="F54">
-        <v>-4.162143704366446</v>
+        <v>-4.095320816970393</v>
       </c>
       <c r="G54">
-        <v>-17.11518722360091</v>
+        <v>-16.77036245550319</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.1318457220907522</v>
       </c>
       <c r="E55">
-        <v>-33.1986050406226</v>
+        <v>-35.61366966399425</v>
       </c>
       <c r="F55">
-        <v>-4.147757319830593</v>
+        <v>-5.059997266418362</v>
       </c>
       <c r="G55">
-        <v>-16.65848422427629</v>
+        <v>-16.53142217593352</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.1300459782121965</v>
       </c>
       <c r="E56">
-        <v>-32.3143253926708</v>
+        <v>-35.40309562263758</v>
       </c>
       <c r="F56">
-        <v>-4.094502832865069</v>
+        <v>-4.946829600965848</v>
       </c>
       <c r="G56">
-        <v>-16.95563051551742</v>
+        <v>-17.66007322445509</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.112652314694901</v>
       </c>
       <c r="E57">
-        <v>-32.65274051950102</v>
+        <v>-37.29641890592651</v>
       </c>
       <c r="F57">
-        <v>-4.302172605850728</v>
+        <v>-4.533705659570229</v>
       </c>
       <c r="G57">
-        <v>-17.10396447422277</v>
+        <v>-17.85785514660777</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.08369153514392805</v>
       </c>
       <c r="E58">
-        <v>-31.22653159434029</v>
+        <v>-34.99062862459694</v>
       </c>
       <c r="F58">
-        <v>-3.920851854796006</v>
+        <v>-4.618979512734108</v>
       </c>
       <c r="G58">
-        <v>-17.13196837893947</v>
+        <v>-17.92562366906942</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.04687010183105975</v>
       </c>
       <c r="E59">
-        <v>-31.65975258875809</v>
+        <v>-34.33843553377525</v>
       </c>
       <c r="F59">
-        <v>-4.148586389877326</v>
+        <v>-5.035571770084539</v>
       </c>
       <c r="G59">
-        <v>-16.96695754708004</v>
+        <v>-17.40452559318767</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.005708317987005676</v>
       </c>
       <c r="E60">
-        <v>-31.6814303938328</v>
+        <v>-33.22161421705557</v>
       </c>
       <c r="F60">
-        <v>-4.256492984278751</v>
+        <v>-5.424339898206615</v>
       </c>
       <c r="G60">
-        <v>-16.99053856295627</v>
+        <v>-17.93380899291527</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.03676350092972934</v>
       </c>
       <c r="E61">
-        <v>-30.91863158961077</v>
+        <v>-34.80629256164071</v>
       </c>
       <c r="F61">
-        <v>-4.33217195515394</v>
+        <v>-5.167516644723461</v>
       </c>
       <c r="G61">
-        <v>-17.05218754198857</v>
+        <v>-17.23698881508177</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.07727987952876633</v>
       </c>
       <c r="E62">
-        <v>-31.43729809584229</v>
+        <v>-33.89808898550639</v>
       </c>
       <c r="F62">
-        <v>-4.183726448582054</v>
+        <v>-4.681159766239049</v>
       </c>
       <c r="G62">
-        <v>-17.28279021261759</v>
+        <v>-17.67974779659498</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.1125809958765295</v>
       </c>
       <c r="E63">
-        <v>-30.39624041350794</v>
+        <v>-32.47800934991506</v>
       </c>
       <c r="F63">
-        <v>-4.003047775513229</v>
+        <v>-5.536632566140849</v>
       </c>
       <c r="G63">
-        <v>-17.31948595464764</v>
+        <v>-18.23104301361319</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.1396293926160876</v>
       </c>
       <c r="E64">
-        <v>-30.6602979971322</v>
+        <v>-33.60380836635494</v>
       </c>
       <c r="F64">
-        <v>-4.463738324079072</v>
+        <v>-5.042505234582333</v>
       </c>
       <c r="G64">
-        <v>-17.55182004059369</v>
+        <v>-18.71386290669712</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.1556737440045747</v>
       </c>
       <c r="E65">
-        <v>-31.83964848294979</v>
+        <v>-33.7763002055441</v>
       </c>
       <c r="F65">
-        <v>-4.261640028503929</v>
+        <v>-5.724093459792543</v>
       </c>
       <c r="G65">
-        <v>-17.48736040839854</v>
+        <v>-18.7358217552591</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.1577027880597115</v>
       </c>
       <c r="E66">
-        <v>-29.86290844420258</v>
+        <v>-34.35207982596037</v>
       </c>
       <c r="F66">
-        <v>-4.082834879533069</v>
+        <v>-5.386780728716053</v>
       </c>
       <c r="G66">
-        <v>-17.60747196638161</v>
+        <v>-18.57912701379432</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.1430209870241255</v>
       </c>
       <c r="E67">
-        <v>-30.15885554178886</v>
+        <v>-32.82644146125023</v>
       </c>
       <c r="F67">
-        <v>-4.541042177223502</v>
+        <v>-5.595777647258851</v>
       </c>
       <c r="G67">
-        <v>-17.35282645877364</v>
+        <v>-18.36039430419637</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.1097005123618768</v>
       </c>
       <c r="E68">
-        <v>-31.30797846360525</v>
+        <v>-33.67317100273043</v>
       </c>
       <c r="F68">
-        <v>-4.378517525063359</v>
+        <v>-5.620987869873773</v>
       </c>
       <c r="G68">
-        <v>-16.94773320913349</v>
+        <v>-18.47954911451858</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.05716098189118744</v>
       </c>
       <c r="E69">
-        <v>-30.60241051389215</v>
+        <v>-32.00669030367073</v>
       </c>
       <c r="F69">
-        <v>-4.49133915077335</v>
+        <v>-5.532389817993387</v>
       </c>
       <c r="G69">
-        <v>-17.69798228142528</v>
+        <v>-18.88602451692138</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.01518728498389695</v>
       </c>
       <c r="E70">
-        <v>-30.53340562696327</v>
+        <v>-33.59499369169901</v>
       </c>
       <c r="F70">
-        <v>-4.63288682623054</v>
+        <v>-5.508285813960399</v>
       </c>
       <c r="G70">
-        <v>-17.1455681000148</v>
+        <v>-18.36262892243537</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.1061739939547008</v>
       </c>
       <c r="E71">
-        <v>-30.83590316220164</v>
+        <v>-32.0689590855132</v>
       </c>
       <c r="F71">
-        <v>-4.359037942303455</v>
+        <v>-6.265254085554258</v>
       </c>
       <c r="G71">
-        <v>-17.68949073211705</v>
+        <v>-18.72839289106898</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.2127774509331094</v>
       </c>
       <c r="E72">
-        <v>-30.8480960784673</v>
+        <v>-33.4857102927089</v>
       </c>
       <c r="F72">
-        <v>-4.667619080662043</v>
+        <v>-5.432903787944354</v>
       </c>
       <c r="G72">
-        <v>-17.04195299045392</v>
+        <v>-18.11282839822412</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.3315424601622248</v>
       </c>
       <c r="E73">
-        <v>-30.40551699251265</v>
+        <v>-31.98693483581227</v>
       </c>
       <c r="F73">
-        <v>-4.851484961885689</v>
+        <v>-5.294373072256077</v>
       </c>
       <c r="G73">
-        <v>-17.25394377406115</v>
+        <v>-18.66822372589273</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.4590263980523082</v>
       </c>
       <c r="E74">
-        <v>-31.19808598486111</v>
+        <v>-33.15244856929942</v>
       </c>
       <c r="F74">
-        <v>-4.812890048726429</v>
+        <v>-5.542255513993616</v>
       </c>
       <c r="G74">
-        <v>-17.10298620801592</v>
+        <v>-17.31137015225811</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.5913519245269075</v>
       </c>
       <c r="E75">
-        <v>-30.72910815967875</v>
+        <v>-32.80572822113915</v>
       </c>
       <c r="F75">
-        <v>-4.870928119409539</v>
+        <v>-5.957780353557042</v>
       </c>
       <c r="G75">
-        <v>-16.50492622470996</v>
+        <v>-17.78257996213582</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.7234729826824641</v>
       </c>
       <c r="E76">
-        <v>-31.79852993896015</v>
+        <v>-34.84994252260065</v>
       </c>
       <c r="F76">
-        <v>-5.054371943006721</v>
+        <v>-5.920859417550402</v>
       </c>
       <c r="G76">
-        <v>-16.84357848064971</v>
+        <v>-18.42310596834678</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.8518377354099705</v>
       </c>
       <c r="E77">
-        <v>-30.57817864947711</v>
+        <v>-33.30599100900349</v>
       </c>
       <c r="F77">
-        <v>-5.034767247479496</v>
+        <v>-5.623861504257338</v>
       </c>
       <c r="G77">
-        <v>-16.71303042785409</v>
+        <v>-18.24266302845603</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.9723878002187444</v>
       </c>
       <c r="E78">
-        <v>-31.27101479451764</v>
+        <v>-34.49132813745923</v>
       </c>
       <c r="F78">
-        <v>-5.105126550184725</v>
+        <v>-5.682630455220423</v>
       </c>
       <c r="G78">
-        <v>-16.66212416909672</v>
+        <v>-16.57342968828133</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.080604663702646</v>
       </c>
       <c r="E79">
-        <v>-32.06330981418864</v>
+        <v>-34.09513194652815</v>
       </c>
       <c r="F79">
-        <v>-5.021912306563874</v>
+        <v>-5.460407216724833</v>
       </c>
       <c r="G79">
-        <v>-16.72996552356023</v>
+        <v>-17.55076232129389</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.172629749947373</v>
       </c>
       <c r="E80">
-        <v>-32.77957854798185</v>
+        <v>-34.94798624910371</v>
       </c>
       <c r="F80">
-        <v>-5.589347801242166</v>
+        <v>-5.751848697813577</v>
       </c>
       <c r="G80">
-        <v>-15.87652178099104</v>
+        <v>-17.32645299773504</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.245230615827647</v>
       </c>
       <c r="E81">
-        <v>-32.67426209222247</v>
+        <v>-35.01900630696601</v>
       </c>
       <c r="F81">
-        <v>-5.213200225560228</v>
+        <v>-5.991247226962108</v>
       </c>
       <c r="G81">
-        <v>-15.738561416733</v>
+        <v>-17.33176642332556</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.294757020961156</v>
       </c>
       <c r="E82">
-        <v>-31.9413783872951</v>
+        <v>-36.00874279337143</v>
       </c>
       <c r="F82">
-        <v>-5.289584737420745</v>
+        <v>-6.252251464062022</v>
       </c>
       <c r="G82">
-        <v>-16.73473436440955</v>
+        <v>-18.48460762810259</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.317845471893866</v>
       </c>
       <c r="E83">
-        <v>-32.99889707264734</v>
+        <v>-37.25182928660998</v>
       </c>
       <c r="F83">
-        <v>-5.45181719583949</v>
+        <v>-5.564301492189491</v>
       </c>
       <c r="G83">
-        <v>-15.73386540788554</v>
+        <v>-17.51085866063629</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.310757945752901</v>
       </c>
       <c r="E84">
-        <v>-34.70276711735136</v>
+        <v>-36.91007214596211</v>
       </c>
       <c r="F84">
-        <v>-5.298566725520161</v>
+        <v>-6.035975041278907</v>
       </c>
       <c r="G84">
-        <v>-16.08547182852045</v>
+        <v>-17.55791806547703</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.268787461287304</v>
       </c>
       <c r="E85">
-        <v>-34.63112213007601</v>
+        <v>-37.90027053671631</v>
       </c>
       <c r="F85">
-        <v>-5.017211075553893</v>
+        <v>-5.402351725276653</v>
       </c>
       <c r="G85">
-        <v>-16.11128580736292</v>
+        <v>-17.77003133926921</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.187607944154852</v>
       </c>
       <c r="E86">
-        <v>-35.18681117555724</v>
+        <v>-37.21658190917127</v>
       </c>
       <c r="F86">
-        <v>-5.261418527714655</v>
+        <v>-5.82210585148726</v>
       </c>
       <c r="G86">
-        <v>-16.21618706386581</v>
+        <v>-16.84609946107786</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.064027741558992</v>
       </c>
       <c r="E87">
-        <v>-36.12838507665408</v>
+        <v>-38.33800415548275</v>
       </c>
       <c r="F87">
-        <v>-5.504764443857419</v>
+        <v>-5.924934292870828</v>
       </c>
       <c r="G87">
-        <v>-15.83641286651001</v>
+        <v>-17.25862157490814</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.892149772102241</v>
       </c>
       <c r="E88">
-        <v>-36.48385670083418</v>
+        <v>-40.71715571573657</v>
       </c>
       <c r="F88">
-        <v>-5.452995473040576</v>
+        <v>-5.989276304950343</v>
       </c>
       <c r="G88">
-        <v>-16.00688940905478</v>
+        <v>-18.00144012773704</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.6670905540422304</v>
       </c>
       <c r="E89">
-        <v>-37.84918255719878</v>
+        <v>-38.55716644779497</v>
       </c>
       <c r="F89">
-        <v>-5.438737368683875</v>
+        <v>-5.485318118921738</v>
       </c>
       <c r="G89">
-        <v>-15.45228364649729</v>
+        <v>-17.35596651121764</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.3878760632899491</v>
       </c>
       <c r="E90">
-        <v>-39.22084827717411</v>
+        <v>-40.38241091708958</v>
       </c>
       <c r="F90">
-        <v>-5.688998536706405</v>
+        <v>-6.220197256333527</v>
       </c>
       <c r="G90">
-        <v>-15.63189232891214</v>
+        <v>-17.0947446048959</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.05324953002290284</v>
       </c>
       <c r="E91">
-        <v>-39.9855648901384</v>
+        <v>-42.26273295150248</v>
       </c>
       <c r="F91">
-        <v>-5.616895573788278</v>
+        <v>-6.155562654586133</v>
       </c>
       <c r="G91">
-        <v>-15.34878937184859</v>
+        <v>-17.03222826293231</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.3395365116739644</v>
       </c>
       <c r="E92">
-        <v>-41.26524824606993</v>
+        <v>-43.05789223098333</v>
       </c>
       <c r="F92">
-        <v>-5.612914137116863</v>
+        <v>-5.601774349707662</v>
       </c>
       <c r="G92">
-        <v>-15.72966763614174</v>
+        <v>-17.57923135765886</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.7895198072573073</v>
       </c>
       <c r="E93">
-        <v>-41.30816685847763</v>
+        <v>-45.11934643299202</v>
       </c>
       <c r="F93">
-        <v>-5.560341435547935</v>
+        <v>-6.025189212141806</v>
       </c>
       <c r="G93">
-        <v>-15.08671003423219</v>
+        <v>-16.74022324891366</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.288520373020615</v>
       </c>
       <c r="E94">
-        <v>-42.61215453440833</v>
+        <v>-46.2430736725734</v>
       </c>
       <c r="F94">
-        <v>-5.891044569986339</v>
+        <v>-5.540708233314232</v>
       </c>
       <c r="G94">
-        <v>-15.66221858132463</v>
+        <v>-17.93726520245826</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.834154703862663</v>
       </c>
       <c r="E95">
-        <v>-44.30296446007424</v>
+        <v>-46.86850574624677</v>
       </c>
       <c r="F95">
-        <v>-5.610829188279187</v>
+        <v>-6.333848743943208</v>
       </c>
       <c r="G95">
-        <v>-16.2512341542173</v>
+        <v>-17.56909943303592</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.426244013310126</v>
       </c>
       <c r="E96">
-        <v>-46.50847394874094</v>
+        <v>-48.82255133750454</v>
       </c>
       <c r="F96">
-        <v>-5.809060865861785</v>
+        <v>-6.089985747819053</v>
       </c>
       <c r="G96">
-        <v>-16.46785639103397</v>
+        <v>-16.90360529236778</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.048909138019389</v>
       </c>
       <c r="E97">
-        <v>-46.84513202765618</v>
+        <v>-49.21600893377948</v>
       </c>
       <c r="F97">
-        <v>-6.066079707025495</v>
+        <v>-6.092959947528249</v>
       </c>
       <c r="G97">
-        <v>-16.6029233384907</v>
+        <v>-17.2040174367834</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.703496688483553</v>
       </c>
       <c r="E98">
-        <v>-49.3070584321777</v>
+        <v>-51.18963904300193</v>
       </c>
       <c r="F98">
-        <v>-6.048902040813681</v>
+        <v>-6.110439705643433</v>
       </c>
       <c r="G98">
-        <v>-16.61740035413393</v>
+        <v>-17.93952796033436</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.365787657159235</v>
       </c>
       <c r="E99">
-        <v>-50.32711418418297</v>
+        <v>-52.83044329443813</v>
       </c>
       <c r="F99">
-        <v>-6.226118336824877</v>
+        <v>-6.293096823327121</v>
       </c>
       <c r="G99">
-        <v>-16.34045832231897</v>
+        <v>-18.37878107412148</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.055324928158063</v>
       </c>
       <c r="E100">
-        <v>-52.12129332178497</v>
+        <v>-53.37258880628092</v>
       </c>
       <c r="F100">
-        <v>-6.097733237157383</v>
+        <v>-5.551197117592188</v>
       </c>
       <c r="G100">
-        <v>-16.50308059557182</v>
+        <v>-17.03249641712099</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.711343571487953</v>
       </c>
       <c r="E101">
-        <v>-53.2744545102977</v>
+        <v>-54.63152043007231</v>
       </c>
       <c r="F101">
-        <v>-6.075631829254468</v>
+        <v>-5.150578909957837</v>
       </c>
       <c r="G101">
-        <v>-17.30411343643603</v>
+        <v>-18.01230864874247</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.402394604776558</v>
       </c>
       <c r="E102">
-        <v>-55.27018130844058</v>
+        <v>-57.12322834390528</v>
       </c>
       <c r="F102">
-        <v>-6.211996827103381</v>
+        <v>-5.897024643523038</v>
       </c>
       <c r="G102">
-        <v>-17.03877155619068</v>
+        <v>-18.38567197466147</v>
       </c>
     </row>
   </sheetData>
